--- a/DataGen_Automation_Kit/data/Shipment_From_SO.xlsx
+++ b/DataGen_Automation_Kit/data/Shipment_From_SO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\DataGen_Automation\DataGen_Automation_Kit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F9ADADA-F12F-4019-8E9C-3BB76616EDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33B63451-0FAE-448C-9479-C5F85F0C721E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{FBB31AA2-1C83-41A2-BFDB-CFAF0FBAD68A}"/>
+    <workbookView xWindow="4470" yWindow="2550" windowWidth="21600" windowHeight="11775" xr2:uid="{4D9827ED-EE19-4FBA-A1A2-A648267A5CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="181">
   <si>
     <t>S/O Date</t>
   </si>
@@ -158,339 +158,408 @@
     <t>Regular SKU</t>
   </si>
   <si>
+    <t>Golden State Apparel</t>
+  </si>
+  <si>
+    <t>wh-Golden-SA</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>90015-260311-000019</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>MAIN</t>
+  </si>
+  <si>
+    <t>AVIANA-06-BLACK-5.5</t>
+  </si>
+  <si>
+    <t>FUR SLIPPER</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>AVIANA-06</t>
+  </si>
+  <si>
+    <t>BLACK</t>
+  </si>
+  <si>
+    <t>WOMEN</t>
+  </si>
+  <si>
+    <t>AMZ eCom</t>
+  </si>
+  <si>
+    <t>AMZ-eCom</t>
+  </si>
+  <si>
+    <t>AMZ-eCom ( Amazon )</t>
+  </si>
+  <si>
+    <t>10001-260311-000010</t>
+  </si>
+  <si>
+    <t>ADELINE-02-PINK-9</t>
+  </si>
+  <si>
+    <t>WOVEN SLIDE SANDAL</t>
+  </si>
+  <si>
+    <t>ADELINE-02</t>
+  </si>
+  <si>
+    <t>PINK</t>
+  </si>
+  <si>
+    <t>10001-260311-000014</t>
+  </si>
+  <si>
+    <t>AVIANA-06-WHITE-8</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>JCPenney</t>
+  </si>
+  <si>
+    <t>JCPenney ( JC Penney (By CommerceHub) )</t>
+  </si>
+  <si>
+    <t>30007-260311-000011</t>
+  </si>
+  <si>
+    <t>F13031C-1742VNTGBJ-30-STD</t>
+  </si>
+  <si>
+    <t>Cayden Vintage Beujolias Corduroy Skinny Jeans</t>
+  </si>
+  <si>
+    <t>Standards &amp; Practices</t>
+  </si>
+  <si>
+    <t>F13031C</t>
+  </si>
+  <si>
+    <t>1742VNTGBJ</t>
+  </si>
+  <si>
+    <t>WMSIZE1</t>
+  </si>
+  <si>
+    <t>Shopify</t>
+  </si>
+  <si>
+    <t>Shopify ( Shopify )</t>
+  </si>
+  <si>
+    <t>20001-260311-000007</t>
+  </si>
+  <si>
+    <t>F13031C-1742VNTGDM-28-STD</t>
+  </si>
+  <si>
+    <t>BOTTOM</t>
+  </si>
+  <si>
+    <t>1742VNTGDM</t>
+  </si>
+  <si>
+    <t>90015-260311-000016</t>
+  </si>
+  <si>
+    <t>ASTRID-01-NUDE-8.5</t>
+  </si>
+  <si>
+    <t>SLIP ON SNEAKER</t>
+  </si>
+  <si>
+    <t>BF</t>
+  </si>
+  <si>
+    <t>ASTRID-01</t>
+  </si>
+  <si>
+    <t>NUDE</t>
+  </si>
+  <si>
+    <t>ADELINE-02-WHITE-10</t>
+  </si>
+  <si>
+    <t>eBay</t>
+  </si>
+  <si>
+    <t>eBay ( eBay )</t>
+  </si>
+  <si>
+    <t>10004-260311-000015</t>
+  </si>
+  <si>
+    <t>CORA-01-FUCH-8</t>
+  </si>
+  <si>
+    <t>CROSS FRONT SANDAL</t>
+  </si>
+  <si>
+    <t>CORA-01</t>
+  </si>
+  <si>
+    <t>FUCH</t>
+  </si>
+  <si>
+    <t>Prepack SKU</t>
+  </si>
+  <si>
+    <t>Walmart eComm</t>
+  </si>
+  <si>
+    <t>Walmart-eComm</t>
+  </si>
+  <si>
+    <t>Walmart-eComm ( Walmart )</t>
+  </si>
+  <si>
+    <t>10002-260311-000018</t>
+  </si>
+  <si>
+    <t>AUSTIN-06-BLUSH-A12</t>
+  </si>
+  <si>
+    <t>SNEAKER</t>
+  </si>
+  <si>
+    <t>AUSTIN-06</t>
+  </si>
+  <si>
+    <t>BLUSH</t>
+  </si>
+  <si>
+    <t>CORA-01-CAME-10</t>
+  </si>
+  <si>
+    <t>CAME</t>
+  </si>
+  <si>
+    <t>Mirakl Kohls</t>
+  </si>
+  <si>
+    <t>Mirakl-Kohls</t>
+  </si>
+  <si>
+    <t>Mirakl-Kohls ( Kohl's (By Mirakl) )</t>
+  </si>
+  <si>
+    <t>10013-260311-000003</t>
+  </si>
+  <si>
+    <t>FA13501DM-1608BLAU2-30-32</t>
+  </si>
+  <si>
+    <t>Maya Basic Dark Handsand Wash Midrise Skinny Jeans</t>
+  </si>
+  <si>
+    <t>Poetic Justice</t>
+  </si>
+  <si>
+    <t>FA13501DM</t>
+  </si>
+  <si>
+    <t>1608BLAU2</t>
+  </si>
+  <si>
+    <t>Women</t>
+  </si>
+  <si>
+    <t>10001-260311-000008</t>
+  </si>
+  <si>
+    <t>CORA-01-TAUP-7</t>
+  </si>
+  <si>
+    <t>TAUP</t>
+  </si>
+  <si>
+    <t>173451-1183CITIZEN-19-34</t>
+  </si>
+  <si>
+    <t>Susan Stretch Denim Skinny Jeans Medium Blue 5 Poc</t>
+  </si>
+  <si>
+    <t>1183CITIZEN</t>
+  </si>
+  <si>
+    <t>JNSIZE</t>
+  </si>
+  <si>
     <t>Etsy VS</t>
   </si>
   <si>
     <t>Etsy-VS</t>
   </si>
   <si>
-    <t>USD</t>
-  </si>
-  <si>
     <t>Etsy-VS ( Etsy )</t>
   </si>
   <si>
-    <t>10008-260308-000007</t>
-  </si>
-  <si>
-    <t>Processing</t>
-  </si>
-  <si>
-    <t>MAIN</t>
-  </si>
-  <si>
-    <t>CAMILA-06-BLACK-8.5</t>
+    <t>10008-260311-000020</t>
+  </si>
+  <si>
+    <t>34478006-BLACK-2X-STD</t>
+  </si>
+  <si>
+    <t>Supersoft longline mongolian cashmere cardigan</t>
+  </si>
+  <si>
+    <t>SWEATERS</t>
+  </si>
+  <si>
+    <t>2X</t>
+  </si>
+  <si>
+    <t>WPSIZE</t>
+  </si>
+  <si>
+    <t>10004-260311-000005</t>
+  </si>
+  <si>
+    <t>ADELINE-02-CAMEL-9.5</t>
+  </si>
+  <si>
+    <t>CAMEL</t>
+  </si>
+  <si>
+    <t>90015-260311-000009</t>
+  </si>
+  <si>
+    <t>F13031C-1742VNTGCO-32-STD</t>
+  </si>
+  <si>
+    <t>1742VNTGCO</t>
+  </si>
+  <si>
+    <t>30007-260311-000017</t>
+  </si>
+  <si>
+    <t>AUSTIN-06-BLACK-9.5</t>
+  </si>
+  <si>
+    <t>FA13512DM-1847DPOCN-26-30</t>
+  </si>
+  <si>
+    <t>Angie Stud Bling Pocket Low Rise Skinny Jeans</t>
+  </si>
+  <si>
+    <t>FA13512DM</t>
+  </si>
+  <si>
+    <t>1847DPOCN</t>
+  </si>
+  <si>
+    <t>ADELINE-03-BROWN-8</t>
+  </si>
+  <si>
+    <t>BUCKLE FRONT FLAT SANDALS</t>
+  </si>
+  <si>
+    <t>BEAST</t>
+  </si>
+  <si>
+    <t>ADELINE-03</t>
+  </si>
+  <si>
+    <t>BROWN</t>
+  </si>
+  <si>
+    <t>CORA-01-LEOP-12</t>
+  </si>
+  <si>
+    <t>LEOP</t>
+  </si>
+  <si>
+    <t>CORA-01-TAUP-11</t>
+  </si>
+  <si>
+    <t>Macys</t>
+  </si>
+  <si>
+    <t>Macys ( Macy's (By CommerceHub) )</t>
+  </si>
+  <si>
+    <t>30005-260311-000002</t>
+  </si>
+  <si>
+    <t>FA13512DM-1847DPOCN-28-32</t>
+  </si>
+  <si>
+    <t>FA13501DM-1464KINGSC-31-32</t>
+  </si>
+  <si>
+    <t>1464KINGSC</t>
+  </si>
+  <si>
+    <t>Harbor West Collective</t>
+  </si>
+  <si>
+    <t>wh-Harbor-WC</t>
+  </si>
+  <si>
+    <t>90016-260311-000004</t>
+  </si>
+  <si>
+    <t>ADELINE-03-BLACK-11</t>
+  </si>
+  <si>
+    <t>30005-260311-000001</t>
+  </si>
+  <si>
+    <t>ADELINE-03-GOLD-6.5</t>
+  </si>
+  <si>
+    <t>GOLD</t>
+  </si>
+  <si>
+    <t>10008-260311-000012</t>
+  </si>
+  <si>
+    <t>FA13501DM-RINSEWSFT-29-30</t>
+  </si>
+  <si>
+    <t>RINSEWSFT</t>
+  </si>
+  <si>
+    <t>CAMILA-06-GREEN-12</t>
   </si>
   <si>
     <t>COSS FRONT SLIP ON SLIDES</t>
   </si>
   <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>CB</t>
   </si>
   <si>
     <t>CAMILA-06</t>
   </si>
   <si>
-    <t>BLACK</t>
-  </si>
-  <si>
-    <t>WOMEN</t>
-  </si>
-  <si>
-    <t>Mirakl Kohls</t>
-  </si>
-  <si>
-    <t>Mirakl-Kohls</t>
-  </si>
-  <si>
-    <t>Mirakl-Kohls ( Kohl's (By Mirakl) )</t>
-  </si>
-  <si>
-    <t>10013-260308-000017</t>
-  </si>
-  <si>
-    <t>FB3601737-3219UNFORGV-30-STD</t>
-  </si>
-  <si>
-    <t>Denim Stretch High-Waist Slit Hem Jeans</t>
-  </si>
-  <si>
-    <t>Standards &amp; Practices</t>
-  </si>
-  <si>
-    <t>BOTTOM</t>
-  </si>
-  <si>
-    <t>FB3601737</t>
-  </si>
-  <si>
-    <t>3219UNFORGV</t>
-  </si>
-  <si>
-    <t>Women</t>
-  </si>
-  <si>
-    <t>WMSIZE1</t>
-  </si>
-  <si>
-    <t>Mirakl HudsonsB</t>
-  </si>
-  <si>
-    <t>Mirakl-HudsonsB</t>
-  </si>
-  <si>
-    <t>Mirakl-HudsonsB ( Hudson's Bay Marketplace (By Mirakl) )</t>
-  </si>
-  <si>
-    <t>10005-260308-000018</t>
-  </si>
-  <si>
-    <t>Shopify</t>
-  </si>
-  <si>
-    <t>Shopify ( Shopify )</t>
-  </si>
-  <si>
-    <t>20001-260308-000006</t>
-  </si>
-  <si>
-    <t>AVIANA-06-BEIGE-6.5</t>
-  </si>
-  <si>
-    <t>FUR SLIPPER</t>
-  </si>
-  <si>
-    <t>AVIANA-06</t>
-  </si>
-  <si>
-    <t>BEIGE</t>
-  </si>
-  <si>
-    <t>Macys</t>
-  </si>
-  <si>
-    <t>Macys ( Macy's (By CommerceHub) )</t>
-  </si>
-  <si>
-    <t>30005-260308-000001</t>
-  </si>
-  <si>
-    <t>AVIANA-06-BEIGE-9</t>
-  </si>
-  <si>
-    <t>AMZ eCom</t>
-  </si>
-  <si>
-    <t>AMZ-eCom</t>
-  </si>
-  <si>
-    <t>AMZ-eCom ( Amazon )</t>
-  </si>
-  <si>
-    <t>10001-260308-000014</t>
-  </si>
-  <si>
-    <t>ADELINE-03-GOLD-5.5</t>
-  </si>
-  <si>
-    <t>BUCKLE FRONT FLAT SANDALS</t>
-  </si>
-  <si>
-    <t>BEAST</t>
-  </si>
-  <si>
-    <t>ADELINE-03</t>
-  </si>
-  <si>
-    <t>GOLD</t>
-  </si>
-  <si>
-    <t>10001-260308-000009</t>
-  </si>
-  <si>
-    <t>FA13501DM-1608BLAU2-31-32</t>
-  </si>
-  <si>
-    <t>Maya Basic Dark Handsand Wash Midrise Skinny Jeans</t>
-  </si>
-  <si>
-    <t>Poetic Justice</t>
-  </si>
-  <si>
-    <t>FA13501DM</t>
-  </si>
-  <si>
-    <t>1608BLAU2</t>
-  </si>
-  <si>
-    <t>10008-260308-000013</t>
-  </si>
-  <si>
-    <t>AVIANA-06-WHITE-5</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>JCPenney</t>
-  </si>
-  <si>
-    <t>JCPenney ( JC Penney (By CommerceHub) )</t>
-  </si>
-  <si>
-    <t>30007-260308-000010</t>
-  </si>
-  <si>
-    <t>CORA-01-YLW-7.5</t>
-  </si>
-  <si>
-    <t>CROSS FRONT SANDAL</t>
-  </si>
-  <si>
-    <t>CORA-01</t>
-  </si>
-  <si>
-    <t>YLW</t>
-  </si>
-  <si>
-    <t>Walmart eComm</t>
-  </si>
-  <si>
-    <t>Walmart-eComm</t>
-  </si>
-  <si>
-    <t>Walmart-eComm ( Walmart )</t>
-  </si>
-  <si>
-    <t>10002-260308-000016</t>
-  </si>
-  <si>
-    <t>F13031C-1742VNTGST-24-STD</t>
-  </si>
-  <si>
-    <t>Cayden Vintage Beujolias Corduroy Skinny Jeans</t>
-  </si>
-  <si>
-    <t>F13031C</t>
-  </si>
-  <si>
-    <t>1742VNTGST</t>
-  </si>
-  <si>
-    <t>10013-260308-000008</t>
-  </si>
-  <si>
-    <t>F13031C-1742VNTGDM-25-STD</t>
-  </si>
-  <si>
-    <t>1742VNTGDM</t>
-  </si>
-  <si>
-    <t>AVIANA-06-BLACK-5</t>
-  </si>
-  <si>
-    <t>Prepack SKU</t>
-  </si>
-  <si>
-    <t>30005-260308-000019</t>
-  </si>
-  <si>
-    <t>CAMILA-06-BLACK-B12</t>
-  </si>
-  <si>
-    <t>F13031C-1742VNTGDM-26-STD</t>
-  </si>
-  <si>
-    <t>CAMILA-06-TAUPE-8.5</t>
-  </si>
-  <si>
-    <t>TAUPE</t>
-  </si>
-  <si>
-    <t>10008-260308-000003</t>
-  </si>
-  <si>
-    <t>AVIANA-06-BLACK-10</t>
-  </si>
-  <si>
-    <t>Squarespace</t>
-  </si>
-  <si>
-    <t>Squarespace ( Squarespace )</t>
-  </si>
-  <si>
-    <t>20006-260308-000004</t>
-  </si>
-  <si>
-    <t>173451-1183CITIZEN-9-STD</t>
-  </si>
-  <si>
-    <t>Susan Stretch Denim Skinny Jeans Medium Blue 5 Poc</t>
-  </si>
-  <si>
-    <t>1183CITIZEN</t>
-  </si>
-  <si>
-    <t>JNSIZE</t>
-  </si>
-  <si>
-    <t>ASTRID-01-BLUSH-A12</t>
-  </si>
-  <si>
-    <t>SLIP ON SNEAKER</t>
-  </si>
-  <si>
-    <t>BF</t>
-  </si>
-  <si>
-    <t>ASTRID-01</t>
-  </si>
-  <si>
-    <t>BLUSH</t>
-  </si>
-  <si>
-    <t>CORA-01-BLK-12</t>
-  </si>
-  <si>
-    <t>BLK</t>
-  </si>
-  <si>
-    <t>20006-260308-000020</t>
-  </si>
-  <si>
-    <t>F13031C-1742VNTGCO-26-STD</t>
-  </si>
-  <si>
-    <t>1742VNTGCO</t>
-  </si>
-  <si>
-    <t>Magento</t>
-  </si>
-  <si>
-    <t>Magento ( Magento 2.x )</t>
-  </si>
-  <si>
-    <t>20003-260308-000005</t>
-  </si>
-  <si>
-    <t>ADELINE-02-CAMEL-12</t>
-  </si>
-  <si>
-    <t>WOVEN SLIDE SANDAL</t>
-  </si>
-  <si>
-    <t>ADELINE-02</t>
-  </si>
-  <si>
-    <t>CAMEL</t>
+    <t>GREEN</t>
   </si>
   <si>
     <t>AVIANA-06-WHITE-12</t>
   </si>
   <si>
+    <t>AVIANA-06-WHITE-9</t>
+  </si>
+  <si>
+    <t>CORA-01-CAME-6</t>
+  </si>
+  <si>
+    <t>CAMILA-06-NUDE-10</t>
+  </si>
+  <si>
     <t>Veeqo Amazon</t>
   </si>
   <si>
@@ -500,61 +569,16 @@
     <t>Veeqo-Amazon ( Amazon(By Veeqo) )</t>
   </si>
   <si>
-    <t>10016-260308-000015</t>
-  </si>
-  <si>
-    <t>AUSTIN-06-WHITE-9.5</t>
-  </si>
-  <si>
-    <t>SNEAKER</t>
-  </si>
-  <si>
-    <t>AUSTIN-06</t>
-  </si>
-  <si>
-    <t>Etsy LS</t>
-  </si>
-  <si>
-    <t>Etsy-LS</t>
-  </si>
-  <si>
-    <t>Etsy-LS ( Etsy )</t>
-  </si>
-  <si>
-    <t>10008-260308-000002</t>
-  </si>
-  <si>
-    <t>AVIANA-06-BEIGE-12</t>
-  </si>
-  <si>
-    <t>10005-260308-000012</t>
-  </si>
-  <si>
-    <t>CAMILA-06-NUDE-6.5</t>
-  </si>
-  <si>
-    <t>NUDE</t>
-  </si>
-  <si>
-    <t>10005-260308-000011</t>
-  </si>
-  <si>
-    <t>CAMILA-06-TAUPE-11</t>
-  </si>
-  <si>
-    <t>AUSTIN-06-WHITE-B12</t>
-  </si>
-  <si>
-    <t>173451-1183CITIZEN-5-STD</t>
-  </si>
-  <si>
-    <t>10001-260305-000011</t>
-  </si>
-  <si>
-    <t>AVIANA-06-BLACK-8.5</t>
-  </si>
-  <si>
-    <t>ADELINE-02-WHITE-8</t>
+    <t>10016-260311-000006</t>
+  </si>
+  <si>
+    <t>ADELINE-02-CAMEL-5.5</t>
+  </si>
+  <si>
+    <t>30007-260311-000013</t>
+  </si>
+  <si>
+    <t>ADELINE-02-CAMEL-A12</t>
   </si>
 </sst>
 </file>
@@ -597,8 +621,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,8 +956,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4A634A-197A-485C-8D7D-FBD7CB87E218}">
-  <dimension ref="A1:AM31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F967FD-BCF5-408C-8EBB-780821EA0022}">
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -1057,13 +1081,13 @@
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B2" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D2">
-        <v>2000374</v>
+        <v>2000446</v>
       </c>
       <c r="E2" t="s">
         <v>39</v>
@@ -1077,29 +1101,26 @@
       <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>44</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>45</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>46</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>47</v>
       </c>
-      <c r="N2" t="s">
-        <v>48</v>
-      </c>
       <c r="O2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1108,87 +1129,87 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="V2" s="2">
-        <v>43.85</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0</v>
-      </c>
-      <c r="X2" s="3">
+        <v>195</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2">
         <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <v>43.85</v>
+        <v>195</v>
       </c>
       <c r="Z2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI2" t="s">
         <v>49</v>
       </c>
-      <c r="AA2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="AJ2" t="s">
         <v>50</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2">
+        <v>5.5</v>
+      </c>
+      <c r="AM2" t="s">
         <v>51</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK2">
-        <v>8.5</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B3" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D3">
-        <v>2000384</v>
+        <v>2000437</v>
       </c>
       <c r="E3" t="s">
         <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
         <v>56</v>
       </c>
-      <c r="J3" t="s">
+      <c r="N3" t="s">
         <v>57</v>
       </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" t="s">
-        <v>58</v>
-      </c>
       <c r="O3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q3">
         <v>2</v>
@@ -1205,91 +1226,85 @@
       <c r="U3">
         <v>2</v>
       </c>
-      <c r="V3" s="2">
-        <v>47.52</v>
-      </c>
-      <c r="W3" s="3">
-        <v>0</v>
-      </c>
-      <c r="X3" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>47.52</v>
+      <c r="V3" s="3">
+        <v>96.7</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>96.7</v>
       </c>
       <c r="Z3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="AI3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AJ3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AK3">
-        <v>30</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B4" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D4">
-        <v>2000385</v>
+        <v>2000441</v>
       </c>
       <c r="E4" t="s">
         <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="J4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="K4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" t="s">
         <v>45</v>
       </c>
-      <c r="L4" t="s">
-        <v>46</v>
-      </c>
       <c r="M4" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="N4" t="s">
+        <v>47</v>
       </c>
       <c r="O4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1298,188 +1313,179 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>4</v>
-      </c>
-      <c r="V4" s="2">
-        <v>79.72</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0</v>
-      </c>
-      <c r="X4" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>79.72</v>
+        <v>2</v>
+      </c>
+      <c r="V4" s="3">
+        <v>38.74</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>38.74</v>
       </c>
       <c r="Z4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI4" t="s">
         <v>49</v>
       </c>
-      <c r="AA4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>62</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>63</v>
-      </c>
       <c r="AK4">
-        <v>30</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="AM4" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B5" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D5">
-        <v>2000373</v>
+        <v>2000438</v>
       </c>
       <c r="E5" t="s">
         <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" t="s">
+        <v>66</v>
+      </c>
+      <c r="O5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5" s="3">
+        <v>50.5</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>50.5</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5">
+        <v>30</v>
+      </c>
+      <c r="AL5">
+        <v>4</v>
+      </c>
+      <c r="AM5" t="s">
         <v>71</v>
-      </c>
-      <c r="J5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" t="s">
-        <v>73</v>
-      </c>
-      <c r="N5" t="s">
-        <v>74</v>
-      </c>
-      <c r="O5" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2">
-        <v>61.05</v>
-      </c>
-      <c r="W5" s="3">
-        <v>0</v>
-      </c>
-      <c r="X5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>61.05</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK5">
-        <v>6.5</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B6" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D6">
-        <v>2000368</v>
+        <v>2000434</v>
       </c>
       <c r="E6" t="s">
         <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" t="s">
         <v>45</v>
       </c>
-      <c r="L6" t="s">
-        <v>46</v>
-      </c>
       <c r="M6" t="s">
-        <v>80</v>
-      </c>
-      <c r="N6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1496,177 +1502,183 @@
       <c r="U6">
         <v>1</v>
       </c>
-      <c r="V6" s="2">
-        <v>37.81</v>
-      </c>
-      <c r="W6" s="3">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>37.81</v>
+      <c r="V6" s="3">
+        <v>30.43</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>30.43</v>
       </c>
       <c r="Z6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>76</v>
       </c>
       <c r="AI6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK6">
-        <v>9</v>
+        <v>28</v>
+      </c>
+      <c r="AL6">
+        <v>4</v>
       </c>
       <c r="AM6" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B7" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D7">
-        <v>2000381</v>
+        <v>2000443</v>
       </c>
       <c r="E7" t="s">
         <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q7">
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>4</v>
+      </c>
+      <c r="U7">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2">
         <v>83</v>
       </c>
-      <c r="J7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" t="s">
-        <v>85</v>
-      </c>
-      <c r="N7" t="s">
-        <v>86</v>
-      </c>
-      <c r="O7" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2">
-        <v>45.55</v>
-      </c>
-      <c r="W7" s="3">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3">
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
         <v>0</v>
       </c>
       <c r="Y7" s="2">
-        <v>45.55</v>
+        <v>83</v>
       </c>
       <c r="Z7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AI7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="AJ7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="AK7">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AM7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B8" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D8">
-        <v>2000376</v>
+        <v>2000443</v>
       </c>
       <c r="E8" t="s">
         <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
-      <c r="I8" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" t="s">
         <v>45</v>
       </c>
-      <c r="L8" t="s">
-        <v>46</v>
-      </c>
       <c r="M8" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
       </c>
       <c r="O8" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1675,99 +1687,90 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="V8" s="2">
-        <v>54.99</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
+        <v>138</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <v>54.99</v>
+        <v>138</v>
       </c>
       <c r="Z8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="AI8" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="AJ8" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="AK8">
-        <v>31</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B9" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D9">
-        <v>2000380</v>
+        <v>2000442</v>
       </c>
       <c r="E9" t="s">
         <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="J9" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="K9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" t="s">
         <v>45</v>
       </c>
-      <c r="L9" t="s">
-        <v>46</v>
-      </c>
       <c r="M9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="Q9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1776,87 +1779,87 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2">
-        <v>105.84</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>105.84</v>
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
+        <v>78.510000000000005</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>78.510000000000005</v>
       </c>
       <c r="Z9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI9" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AK9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AM9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B10" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D10">
-        <v>2000377</v>
+        <v>2000445</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" t="s">
         <v>45</v>
       </c>
-      <c r="L10" t="s">
-        <v>46</v>
-      </c>
       <c r="M10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="N10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -1873,82 +1876,82 @@
       <c r="U10">
         <v>1</v>
       </c>
-      <c r="V10" s="2">
-        <v>18.920000000000002</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>18.920000000000002</v>
+      <c r="V10" s="3">
+        <v>29.04</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>29.04</v>
       </c>
       <c r="Z10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI10" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s">
-        <v>105</v>
-      </c>
-      <c r="AK10">
-        <v>7.5</v>
+        <v>100</v>
       </c>
       <c r="AM10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B11" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D11">
-        <v>2000383</v>
+        <v>2000434</v>
       </c>
       <c r="E11" t="s">
         <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" t="s">
         <v>45</v>
       </c>
-      <c r="L11" t="s">
-        <v>46</v>
-      </c>
       <c r="M11" t="s">
-        <v>110</v>
+        <v>101</v>
+      </c>
+      <c r="N11" t="s">
+        <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1957,194 +1960,188 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U11">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2">
-        <v>61.68</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>61.68</v>
+        <v>2</v>
+      </c>
+      <c r="V11" s="3">
+        <v>33.479999999999997</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>33.479999999999997</v>
       </c>
       <c r="Z11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB11" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AI11" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="AK11">
-        <v>24</v>
-      </c>
-      <c r="AL11">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B12" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D12">
-        <v>2000375</v>
+        <v>2000430</v>
       </c>
       <c r="E12" t="s">
         <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="J12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="K12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" t="s">
         <v>45</v>
       </c>
-      <c r="L12" t="s">
-        <v>46</v>
-      </c>
       <c r="M12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q12">
+        <v>4</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>4</v>
+      </c>
+      <c r="V12" s="3">
+        <v>52.8</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>52.8</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>111</v>
       </c>
-      <c r="Q12">
-        <v>2</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>2</v>
-      </c>
-      <c r="U12">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2">
-        <v>105.26</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="2">
-        <v>105.26</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI12" t="s">
+      <c r="AK12">
+        <v>30</v>
+      </c>
+      <c r="AL12" t="s">
         <v>112</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK12">
-        <v>25</v>
-      </c>
-      <c r="AL12">
-        <v>4</v>
-      </c>
       <c r="AM12" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B13" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D13">
-        <v>2000374</v>
+        <v>2000435</v>
       </c>
       <c r="E13" t="s">
         <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" t="s">
         <v>44</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>45</v>
       </c>
-      <c r="L13" t="s">
-        <v>46</v>
-      </c>
       <c r="M13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N13" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="O13" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2153,87 +2150,84 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2">
-        <v>18.2</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="2">
-        <v>18.2</v>
+        <v>4</v>
+      </c>
+      <c r="V13" s="3">
+        <v>57.32</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>57.32</v>
       </c>
       <c r="Z13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI13" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="AK13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B14" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D14">
-        <v>2000386</v>
+        <v>2000435</v>
       </c>
       <c r="E14" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="J14" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" t="s">
         <v>45</v>
       </c>
-      <c r="L14" t="s">
-        <v>46</v>
-      </c>
       <c r="M14" t="s">
-        <v>120</v>
-      </c>
-      <c r="N14" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="O14" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -2250,82 +2244,91 @@
       <c r="U14">
         <v>1</v>
       </c>
-      <c r="V14" s="2">
-        <v>46.07</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="2">
-        <v>46.07</v>
+      <c r="V14" s="3">
+        <v>44.39</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>44.39</v>
       </c>
       <c r="Z14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>51</v>
+        <v>68</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI14">
+        <v>173451</v>
       </c>
       <c r="AJ14" t="s">
-        <v>52</v>
+        <v>118</v>
+      </c>
+      <c r="AK14">
+        <v>19</v>
+      </c>
+      <c r="AL14">
+        <v>4</v>
       </c>
       <c r="AM14" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B15" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D15">
-        <v>2000377</v>
+        <v>2000447</v>
       </c>
       <c r="E15" t="s">
         <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="J15" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="K15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" t="s">
         <v>45</v>
       </c>
-      <c r="L15" t="s">
-        <v>46</v>
-      </c>
       <c r="M15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O15" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2334,96 +2337,96 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2">
-        <v>56.24</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="2">
-        <v>56.24</v>
+        <v>2</v>
+      </c>
+      <c r="V15" s="3">
+        <v>45.88</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>45.88</v>
       </c>
       <c r="Z15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG15" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AH15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI15" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI15">
+        <v>34478006</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL15" t="s">
         <v>112</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK15">
-        <v>26</v>
-      </c>
-      <c r="AL15">
-        <v>4</v>
-      </c>
       <c r="AM15" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B16" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D16">
-        <v>2000373</v>
+        <v>2000432</v>
       </c>
       <c r="E16" t="s">
         <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="J16" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="K16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" t="s">
         <v>45</v>
       </c>
-      <c r="L16" t="s">
-        <v>46</v>
-      </c>
       <c r="M16" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="N16" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="O16" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="Q16">
         <v>1</v>
@@ -2440,52 +2443,49 @@
       <c r="U16">
         <v>1</v>
       </c>
-      <c r="V16" s="2">
-        <v>34.99</v>
-      </c>
-      <c r="W16" s="3">
-        <v>0</v>
-      </c>
-      <c r="X16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="2">
-        <v>34.99</v>
+      <c r="V16" s="3">
+        <v>37.590000000000003</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>37.590000000000003</v>
       </c>
       <c r="Z16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI16" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK16">
+        <v>9.5</v>
+      </c>
+      <c r="AM16" t="s">
         <v>51</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>123</v>
-      </c>
-      <c r="AK16">
-        <v>8.5</v>
-      </c>
-      <c r="AM16" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B17" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D17">
-        <v>2000370</v>
+        <v>2000436</v>
       </c>
       <c r="E17" t="s">
         <v>39</v>
@@ -2499,29 +2499,23 @@
       <c r="H17" t="s">
         <v>42</v>
       </c>
-      <c r="I17" t="s">
-        <v>43</v>
-      </c>
       <c r="J17" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K17" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" t="s">
         <v>45</v>
       </c>
-      <c r="L17" t="s">
-        <v>46</v>
-      </c>
       <c r="M17" t="s">
-        <v>125</v>
-      </c>
-      <c r="N17" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="O17" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2530,87 +2524,96 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="V17" s="2">
-        <v>140.46</v>
-      </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3">
+        <v>408</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2">
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <v>140.46</v>
+        <v>408</v>
       </c>
       <c r="Z17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>68</v>
       </c>
       <c r="AI17" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="AJ17" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="AK17">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="AL17">
+        <v>4</v>
       </c>
       <c r="AM17" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B18" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D18">
-        <v>2000371</v>
+        <v>2000444</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="J18" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K18" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" t="s">
         <v>45</v>
       </c>
-      <c r="L18" t="s">
-        <v>46</v>
-      </c>
       <c r="M18" t="s">
-        <v>129</v>
+        <v>136</v>
+      </c>
+      <c r="N18" t="s">
+        <v>98</v>
       </c>
       <c r="O18" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -2619,99 +2622,87 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2">
-        <v>90.76</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="2">
-        <v>90.76</v>
+        <v>1</v>
+      </c>
+      <c r="V18" s="3">
+        <v>69.739999999999995</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>69.739999999999995</v>
       </c>
       <c r="Z18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB18" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI18">
-        <v>173451</v>
+        <v>48</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>99</v>
       </c>
       <c r="AJ18" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="AK18">
-        <v>9</v>
-      </c>
-      <c r="AL18">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="AM18" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B19" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D19">
-        <v>2000368</v>
+        <v>2000432</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J19" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="K19" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" t="s">
         <v>45</v>
       </c>
-      <c r="L19" t="s">
-        <v>46</v>
-      </c>
       <c r="M19" t="s">
-        <v>133</v>
-      </c>
-      <c r="N19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -2720,90 +2711,99 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2">
-        <v>38.119999999999997</v>
-      </c>
-      <c r="W19" s="3">
-        <v>0</v>
-      </c>
-      <c r="X19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="2">
-        <v>38.119999999999997</v>
+        <v>2</v>
+      </c>
+      <c r="V19" s="3">
+        <v>92.86</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>92.86</v>
       </c>
       <c r="Z19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG19" t="s">
-        <v>135</v>
+        <v>109</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>76</v>
       </c>
       <c r="AI19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AJ19" t="s">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="AK19">
+        <v>26</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>112</v>
       </c>
       <c r="AM19" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B20" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D20">
-        <v>2000376</v>
+        <v>2000445</v>
       </c>
       <c r="E20" t="s">
         <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J20" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" t="s">
         <v>45</v>
       </c>
-      <c r="L20" t="s">
-        <v>46</v>
-      </c>
       <c r="M20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="N20" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="O20" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2812,87 +2812,90 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2">
-        <v>18.02</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="2">
-        <v>18.02</v>
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
+        <v>75.44</v>
+      </c>
+      <c r="W20" s="2">
+        <v>0</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>75.44</v>
       </c>
       <c r="Z20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB20" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>143</v>
       </c>
       <c r="AI20" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="AJ20" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AK20">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AM20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B21" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D21">
-        <v>2000387</v>
+        <v>2000443</v>
       </c>
       <c r="E21" t="s">
         <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="G21" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
-      <c r="I21" t="s">
-        <v>127</v>
-      </c>
       <c r="J21" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" t="s">
         <v>45</v>
       </c>
-      <c r="L21" t="s">
-        <v>46</v>
-      </c>
       <c r="M21" t="s">
-        <v>141</v>
+        <v>146</v>
+      </c>
+      <c r="N21" t="s">
+        <v>89</v>
       </c>
       <c r="O21" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="Q21">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2901,96 +2904,87 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="U21">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="V21" s="2">
-        <v>65.040000000000006</v>
-      </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
+        <v>172</v>
+      </c>
+      <c r="W21" s="2">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2">
         <v>0</v>
       </c>
       <c r="Y21" s="2">
-        <v>65.040000000000006</v>
+        <v>172</v>
       </c>
       <c r="Z21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB21" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AI21" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="AJ21" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="AK21">
-        <v>26</v>
-      </c>
-      <c r="AL21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AM21" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B22" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D22">
-        <v>2000372</v>
+        <v>2000446</v>
       </c>
       <c r="E22" t="s">
         <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
-      <c r="I22" t="s">
-        <v>144</v>
-      </c>
       <c r="J22" t="s">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="K22" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" t="s">
         <v>45</v>
       </c>
-      <c r="L22" t="s">
-        <v>46</v>
-      </c>
       <c r="M22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N22" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="O22" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2999,87 +2993,84 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U22">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="V22" s="2">
-        <v>97.68</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
+        <v>129</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2">
         <v>0</v>
       </c>
       <c r="Y22" s="2">
-        <v>97.68</v>
+        <v>129</v>
       </c>
       <c r="Z22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI22" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="AK22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B23" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D23">
-        <v>2000381</v>
+        <v>2000429</v>
       </c>
       <c r="E23" t="s">
         <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="K23" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" t="s">
         <v>45</v>
       </c>
-      <c r="L23" t="s">
-        <v>46</v>
-      </c>
       <c r="M23" t="s">
-        <v>150</v>
-      </c>
-      <c r="N23" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="O23" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -3096,82 +3087,88 @@
       <c r="U23">
         <v>1</v>
       </c>
-      <c r="V23" s="2">
-        <v>20.149999999999999</v>
-      </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="2">
-        <v>20.149999999999999</v>
+      <c r="V23" s="3">
+        <v>35.15</v>
+      </c>
+      <c r="W23" s="2">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>35.15</v>
       </c>
       <c r="Z23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB23" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>76</v>
       </c>
       <c r="AI23" t="s">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AJ23" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="AK23">
-        <v>12</v>
+        <v>28</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>112</v>
       </c>
       <c r="AM23" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B24" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D24">
-        <v>2000382</v>
+        <v>2000447</v>
       </c>
       <c r="E24" t="s">
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G24" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24" t="s">
+        <v>122</v>
+      </c>
+      <c r="J24" t="s">
+        <v>123</v>
+      </c>
+      <c r="K24" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" t="s">
         <v>153</v>
       </c>
-      <c r="J24" t="s">
-        <v>154</v>
-      </c>
-      <c r="K24" t="s">
-        <v>45</v>
-      </c>
-      <c r="L24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M24" t="s">
-        <v>155</v>
-      </c>
-      <c r="N24" t="s">
-        <v>156</v>
-      </c>
       <c r="O24" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="Q24">
         <v>1</v>
@@ -3188,85 +3185,91 @@
       <c r="U24">
         <v>1</v>
       </c>
-      <c r="V24" s="2">
-        <v>56.94</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="2">
-        <v>56.94</v>
+      <c r="V24" s="3">
+        <v>77.510000000000005</v>
+      </c>
+      <c r="W24" s="2">
+        <v>0</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>77.510000000000005</v>
       </c>
       <c r="Z24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>76</v>
       </c>
       <c r="AI24" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="AJ24" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="AK24">
-        <v>9.5</v>
+        <v>31</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>112</v>
       </c>
       <c r="AM24" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B25" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D25">
-        <v>2000369</v>
+        <v>2000431</v>
       </c>
       <c r="E25" t="s">
         <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G25" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
-      <c r="I25" t="s">
-        <v>160</v>
-      </c>
       <c r="J25" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K25" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25" t="s">
         <v>45</v>
       </c>
-      <c r="L25" t="s">
-        <v>46</v>
-      </c>
       <c r="M25" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N25" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="O25" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -3275,87 +3278,90 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="V25" s="2">
-        <v>42.4</v>
-      </c>
-      <c r="W25" s="3">
-        <v>0</v>
-      </c>
-      <c r="X25" s="3">
+        <v>296</v>
+      </c>
+      <c r="W25" s="2">
+        <v>0</v>
+      </c>
+      <c r="X25" s="2">
         <v>0</v>
       </c>
       <c r="Y25" s="2">
-        <v>42.4</v>
+        <v>296</v>
       </c>
       <c r="Z25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB25" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>143</v>
       </c>
       <c r="AI25" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="AJ25" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AK25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B26" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D26">
-        <v>2000379</v>
+        <v>2000428</v>
       </c>
       <c r="E26" t="s">
         <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="G26" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K26" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26" t="s">
         <v>45</v>
       </c>
-      <c r="L26" t="s">
-        <v>46</v>
-      </c>
       <c r="M26" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N26" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="O26" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="Q26">
         <v>3</v>
@@ -3372,88 +3378,85 @@
       <c r="U26">
         <v>3</v>
       </c>
-      <c r="V26" s="2">
-        <v>45.54</v>
-      </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="2">
-        <v>45.54</v>
+      <c r="V26" s="3">
+        <v>89.94</v>
+      </c>
+      <c r="W26" s="2">
+        <v>0</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>89.94</v>
       </c>
       <c r="Z26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG26" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="AI26" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="AJ26" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AK26">
         <v>6.5</v>
       </c>
       <c r="AM26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B27" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D27">
-        <v>2000378</v>
+        <v>2000439</v>
       </c>
       <c r="E27" t="s">
         <v>39</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G27" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="J27" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" t="s">
         <v>45</v>
       </c>
-      <c r="L27" t="s">
-        <v>46</v>
-      </c>
       <c r="M27" t="s">
-        <v>167</v>
-      </c>
-      <c r="N27" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="O27" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="Q27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -3462,90 +3465,96 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U27">
-        <v>4</v>
-      </c>
-      <c r="V27" s="2">
-        <v>125.2</v>
-      </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="2">
-        <v>125.2</v>
+        <v>1</v>
+      </c>
+      <c r="V27" s="3">
+        <v>17.03</v>
+      </c>
+      <c r="W27" s="2">
+        <v>0</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>17.03</v>
       </c>
       <c r="Z27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG27" t="s">
-        <v>50</v>
+        <v>109</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>76</v>
       </c>
       <c r="AI27" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="AJ27" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="AK27">
-        <v>11</v>
+        <v>29</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>112</v>
       </c>
       <c r="AM27" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B28" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D28">
-        <v>2000379</v>
+        <v>2000438</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J28" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="K28" t="s">
+        <v>44</v>
+      </c>
+      <c r="L28" t="s">
         <v>45</v>
       </c>
-      <c r="L28" t="s">
-        <v>46</v>
-      </c>
       <c r="M28" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N28" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="O28" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="Q28">
         <v>1</v>
@@ -3562,79 +3571,88 @@
       <c r="U28">
         <v>1</v>
       </c>
-      <c r="V28" s="2">
-        <v>69.03</v>
-      </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="2">
-        <v>69.03</v>
+      <c r="V28" s="3">
+        <v>25.18</v>
+      </c>
+      <c r="W28" s="2">
+        <v>0</v>
+      </c>
+      <c r="X28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>25.18</v>
       </c>
       <c r="Z28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB28" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>167</v>
       </c>
       <c r="AI28" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AJ28" t="s">
-        <v>98</v>
+        <v>169</v>
+      </c>
+      <c r="AK28">
+        <v>12</v>
       </c>
       <c r="AM28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="B29" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D29">
-        <v>2000369</v>
+        <v>2000429</v>
       </c>
       <c r="E29" t="s">
         <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G29" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="J29" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="K29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29" t="s">
         <v>45</v>
       </c>
-      <c r="L29" t="s">
-        <v>46</v>
-      </c>
       <c r="M29" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="N29" t="s">
+        <v>47</v>
       </c>
       <c r="O29" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3643,99 +3661,90 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>1</v>
-      </c>
-      <c r="V29" s="2">
-        <v>32.28</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="2">
-        <v>32.28</v>
+        <v>3</v>
+      </c>
+      <c r="V29" s="3">
+        <v>41.1</v>
+      </c>
+      <c r="W29" s="2">
+        <v>0</v>
+      </c>
+      <c r="X29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>41.1</v>
       </c>
       <c r="Z29" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI29" t="s">
         <v>49</v>
       </c>
-      <c r="AA29" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI29">
-        <v>173451</v>
-      </c>
       <c r="AJ29" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="AK29">
-        <v>5</v>
-      </c>
-      <c r="AL29">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AM29" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B30" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D30">
-        <v>2000318</v>
+        <v>2000441</v>
       </c>
       <c r="E30" t="s">
         <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="J30" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="K30" t="s">
+        <v>44</v>
+      </c>
+      <c r="L30" t="s">
         <v>45</v>
-      </c>
-      <c r="L30" t="s">
-        <v>46</v>
       </c>
       <c r="M30" t="s">
         <v>171</v>
       </c>
       <c r="N30" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="O30" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="Q30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -3744,135 +3753,411 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V30" s="3">
-        <v>65</v>
-      </c>
-      <c r="W30" s="3">
-        <v>0</v>
-      </c>
-      <c r="X30" s="3">
+        <v>29.52</v>
+      </c>
+      <c r="W30" s="2">
+        <v>0</v>
+      </c>
+      <c r="X30" s="2">
         <v>0</v>
       </c>
       <c r="Y30" s="3">
-        <v>65</v>
+        <v>29.52</v>
       </c>
       <c r="Z30" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI30" t="s">
         <v>49</v>
       </c>
-      <c r="AA30" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>75</v>
-      </c>
       <c r="AJ30" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AK30">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AM30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B31" s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="D31">
-        <v>2000318</v>
+        <v>2000438</v>
       </c>
       <c r="E31" t="s">
         <v>39</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="H31" t="s">
         <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="J31" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="K31" t="s">
+        <v>44</v>
+      </c>
+      <c r="L31" t="s">
         <v>45</v>
-      </c>
-      <c r="L31" t="s">
-        <v>46</v>
       </c>
       <c r="M31" t="s">
         <v>172</v>
       </c>
       <c r="N31" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="O31" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="Q31">
+        <v>2</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>2</v>
+      </c>
+      <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31" s="3">
+        <v>29.42</v>
+      </c>
+      <c r="W31" s="2">
+        <v>0</v>
+      </c>
+      <c r="X31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>29.42</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK31">
+        <v>6</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D32">
+        <v>2000439</v>
+      </c>
+      <c r="E32" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32" t="s">
+        <v>122</v>
+      </c>
+      <c r="J32" t="s">
+        <v>162</v>
+      </c>
+      <c r="K32" t="s">
+        <v>44</v>
+      </c>
+      <c r="L32" t="s">
+        <v>45</v>
+      </c>
+      <c r="M32" t="s">
+        <v>173</v>
+      </c>
+      <c r="N32" t="s">
+        <v>166</v>
+      </c>
+      <c r="O32" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q32">
+        <v>2</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>2</v>
+      </c>
+      <c r="U32">
+        <v>2</v>
+      </c>
+      <c r="V32" s="3">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="W32" s="2">
+        <v>0</v>
+      </c>
+      <c r="X32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>167</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK32">
+        <v>10</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D33">
+        <v>2000433</v>
+      </c>
+      <c r="E33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" t="s">
+        <v>174</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" t="s">
+        <v>177</v>
+      </c>
+      <c r="K33" t="s">
+        <v>44</v>
+      </c>
+      <c r="L33" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" t="s">
+        <v>178</v>
+      </c>
+      <c r="N33" t="s">
+        <v>57</v>
+      </c>
+      <c r="O33" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q33">
         <v>3</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
         <v>3</v>
       </c>
-      <c r="U31">
+      <c r="U33">
         <v>3</v>
       </c>
-      <c r="V31" s="2">
-        <v>34.5</v>
-      </c>
-      <c r="W31" s="3">
-        <v>0</v>
-      </c>
-      <c r="X31" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="2">
-        <v>34.5</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>148</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK31">
-        <v>8</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>53</v>
+      <c r="V33" s="3">
+        <v>123.03</v>
+      </c>
+      <c r="W33" s="2">
+        <v>0</v>
+      </c>
+      <c r="X33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>123.03</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK33">
+        <v>5.5</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D34">
+        <v>2000440</v>
+      </c>
+      <c r="E34" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" t="s">
+        <v>179</v>
+      </c>
+      <c r="K34" t="s">
+        <v>44</v>
+      </c>
+      <c r="L34" t="s">
+        <v>45</v>
+      </c>
+      <c r="M34" t="s">
+        <v>180</v>
+      </c>
+      <c r="N34" t="s">
+        <v>57</v>
+      </c>
+      <c r="O34" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q34">
+        <v>4</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>4</v>
+      </c>
+      <c r="U34">
+        <v>4</v>
+      </c>
+      <c r="V34" s="3">
+        <v>120.28</v>
+      </c>
+      <c r="W34" s="2">
+        <v>0</v>
+      </c>
+      <c r="X34" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>120.28</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
